--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487953_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487953_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3044</v>
+        <v>2.7285</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5007</v>
+        <v>-0.9081</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8051</v>
+        <v>3.6366</v>
       </c>
       <c r="G2" t="n">
         <v>0.8588</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4382</v>
+        <v>-0.1377</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4554</v>
+        <v>0.0479</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0172</v>
+        <v>-0.1856</v>
       </c>
       <c r="V2" t="n">
         <v>3.5932</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4646</v>
+        <v>2.3443</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2214</v>
+        <v>-2.3101</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7568</v>
+        <v>4.6544</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6221</v>
+        <v>2.8034</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1024</v>
+        <v>2.1684</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4803</v>
+        <v>0.6351</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1968</v>
+        <v>0.9486</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1566</v>
+        <v>0.8682</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0402</v>
+        <v>0.0804</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5747</v>
+        <v>1.8549</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0542</v>
+        <v>1.3002</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5205</v>
+        <v>0.5547</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7929</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>-3.1716</v>
       </c>
       <c r="R3" t="n">
-        <v>1.784</v>
+        <v>2.7751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2323</v>
+        <v>-0.5626</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.121</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1113</v>
+        <v>-0.4756</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.7181</v>
+        <v>0.4999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.8548</v>
+        <v>0.4999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUÑOZ</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1133</v>
+        <v>2.2536</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1133</v>
+        <v>3.8139</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.5602</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1133</v>
+        <v>3.6221</v>
       </c>
       <c r="H4" t="n">
-        <v>0.908</v>
+        <v>4.1024</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2053</v>
+        <v>-0.4803</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1133</v>
+        <v>4.1968</v>
       </c>
       <c r="K4" t="n">
-        <v>0.908</v>
+        <v>4.1566</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2053</v>
+        <v>0.0402</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.5747</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.0542</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.5205</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.4432</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.5285</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.0852</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.7181</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.8548</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0349</v>
+        <v>2.1681</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6159</v>
+        <v>0.4122</v>
       </c>
       <c r="F5" t="n">
-        <v>1.419</v>
+        <v>1.756</v>
       </c>
       <c r="G5" t="n">
         <v>2.6999</v>
@@ -844,13 +844,13 @@
         <v>1.784</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5352</v>
+        <v>-0.402</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7453</v>
+        <v>0.5416</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2805</v>
+        <v>-0.9435</v>
       </c>
       <c r="V5" t="n">
         <v>0.2666</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GARCIA TEJON</t>
+          <t>J. LOPEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9657</v>
+        <v>2.1133</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8433</v>
+        <v>2.1133</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8089</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.522</v>
+        <v>2.1133</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1127</v>
+        <v>0.908</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4093</v>
+        <v>1.2053</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7333</v>
+        <v>2.1133</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8538</v>
+        <v>0.908</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1205</v>
+        <v>1.2053</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2552</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9665</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2888</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5491</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8811</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.332</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2947</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>A. GARCIA TEJON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7997</v>
+        <v>1.4459</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0232</v>
+        <v>-1.2507</v>
       </c>
       <c r="F7" t="n">
-        <v>4.8228</v>
+        <v>2.6966</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8034</v>
+        <v>0.522</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1684</v>
+        <v>0.1127</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6351</v>
+        <v>0.4093</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9486</v>
+        <v>-0.7333</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8682</v>
+        <v>-0.8538</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0804</v>
+        <v>0.1205</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8549</v>
+        <v>1.2552</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3002</v>
+        <v>0.9665</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5547</v>
+        <v>0.2888</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1716</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7751</v>
+        <v>2.1805</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1072</v>
+        <v>0.0293</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8001</v>
+        <v>0.4737</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3071</v>
+        <v>-0.4444</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4999</v>
+        <v>-0.2947</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4999</v>
+        <v>-0.2947</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2223</v>
+        <v>-0.1662</v>
       </c>
       <c r="E8" t="n">
         <v>-1.711</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4887</v>
+        <v>1.5448</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5979</v>
@@ -1078,13 +1078,13 @@
         <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2981</v>
+        <v>0.3542</v>
       </c>
       <c r="T8" t="n">
         <v>0.503</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2049</v>
+        <v>-0.1488</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1207</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CASIN LORENTE</t>
+          <t>M. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2624</v>
+        <v>-0.3039</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1882</v>
+        <v>-1.2134</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9258</v>
+        <v>0.9096</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0463</v>
+        <v>-0.9564</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8499</v>
+        <v>0.0901</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8036</v>
+        <v>-1.0464</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5782</v>
+        <v>-1.2979</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1009</v>
+        <v>0.0202</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6791</v>
+        <v>-1.3181</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6246</v>
+        <v>0.3415</v>
       </c>
       <c r="N9" t="n">
-        <v>0.749</v>
+        <v>0.0699</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1244</v>
+        <v>0.2717</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3652</v>
+        <v>0.0578</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2534</v>
+        <v>0.2827</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1119</v>
+        <v>-0.2249</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ</t>
+          <t>J. CASIN LORENTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.7084</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6209</v>
+        <v>-2.4938</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8815</v>
+        <v>1.7854</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9564</v>
+        <v>0.0463</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0901</v>
+        <v>0.8499</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0464</v>
+        <v>-0.8036</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2979</v>
+        <v>-0.5782</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0202</v>
+        <v>0.1009</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3181</v>
+        <v>-0.6791</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3415</v>
+        <v>0.6246</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0699</v>
+        <v>0.749</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2717</v>
+        <v>-0.1244</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3777</v>
+        <v>-0.0808</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1248</v>
+        <v>-0.0522</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2529</v>
+        <v>-0.0285</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4386</v>
+        <v>-1.2492</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.707</v>
+        <v>-1.8671</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2684</v>
+        <v>0.6179</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2659</v>
+        <v>0.4529</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5684</v>
+        <v>0.8529</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3025</v>
+        <v>-0.4</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4763</v>
+        <v>0.6861</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2565</v>
+        <v>0.5655</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.7328</v>
+        <v>0.1205</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7422</v>
+        <v>-0.2331</v>
       </c>
       <c r="N11" t="n">
-        <v>1.3119</v>
+        <v>0.2874</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4303</v>
+        <v>-0.5205</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9645</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7751</v>
+        <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0461</v>
+        <v>-0.2533</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4733</v>
+        <v>-0.2339</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5194</v>
+        <v>-0.0194</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5613</v>
+        <v>-0.4577</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2071</v>
+        <v>-0.337</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7684</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8075</v>
+        <v>-1.4565</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1727</v>
+        <v>-0.7806</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3652</v>
+        <v>-0.6758</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4529</v>
+        <v>0.1855</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8529</v>
+        <v>0.2352</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4</v>
+        <v>-0.0498</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6861</v>
+        <v>0.4436</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5655</v>
+        <v>0.3632</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1205</v>
+        <v>0.0804</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2331</v>
+        <v>-0.2581</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2874</v>
+        <v>-0.128</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5205</v>
+        <v>-0.1301</v>
       </c>
       <c r="P12" t="n">
+        <v>-0.5947</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-0.9911</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-1.9822</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.9911</v>
+        <v>0.3964</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8116</v>
+        <v>-0.1771</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5395</v>
+        <v>-0.233</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2721</v>
+        <v>0.0559</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4577</v>
+        <v>-0.8701</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1207</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8567</v>
+        <v>-1.7298</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9843</v>
+        <v>-4.6051</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8724</v>
+        <v>2.8753</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1855</v>
+        <v>0.2659</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2352</v>
+        <v>1.5684</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0498</v>
+        <v>-1.3025</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4436</v>
+        <v>-1.4763</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3632</v>
+        <v>0.2565</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0804</v>
+        <v>-1.7328</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2581</v>
+        <v>1.7422</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.128</v>
+        <v>1.3119</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1301</v>
+        <v>0.4303</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5947</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3964</v>
+        <v>2.7751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5774</v>
+        <v>-0.2451</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4368</v>
+        <v>-0.3715</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1406</v>
+        <v>0.1263</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8701</v>
+        <v>-0.5613</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8701</v>
+        <v>-1.7684</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.3076</v>
+        <v>-2.3919</v>
       </c>
       <c r="E14" t="n">
         <v>-1.8191</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4885</v>
+        <v>-0.5727</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5099</v>
@@ -1546,13 +1546,13 @@
         <v>0.3964</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.203</v>
+        <v>-0.2873</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2496</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0466</v>
+        <v>-0.0377</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.048099999999999</v>
+        <v>5.047799999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.6198</v>
+        <v>-12.6196</v>
       </c>
       <c r="F15" t="n">
-        <v>17.6677</v>
+        <v>17.6679</v>
       </c>
       <c r="G15" t="n">
         <v>10.5059</v>
@@ -1600,19 +1600,19 @@
         <v>2.397599999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>5.256400000000001</v>
+        <v>5.2564</v>
       </c>
       <c r="L15" t="n">
         <v>-2.859</v>
       </c>
       <c r="M15" t="n">
-        <v>8.108599999999999</v>
+        <v>8.108600000000001</v>
       </c>
       <c r="N15" t="n">
         <v>7.937599999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1711999999999999</v>
+        <v>0.1712000000000001</v>
       </c>
       <c r="P15" t="n">
         <v>-2.9733</v>
@@ -1624,16 +1624,16 @@
         <v>18.8311</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.147699999999999</v>
+        <v>-2.1478</v>
       </c>
       <c r="T15" t="n">
-        <v>0.09309999999999974</v>
+        <v>0.09320000000000006</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.240699999999999</v>
+        <v>-2.241000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3369</v>
+        <v>-0.3369000000000004</v>
       </c>
       <c r="W15" t="n">
         <v>6.6944</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2074</v>
+        <v>3.5102</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6495</v>
+        <v>1.6308</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5579</v>
+        <v>1.8795</v>
       </c>
       <c r="G16" t="n">
         <v>-0.168</v>
@@ -1702,13 +1702,13 @@
         <v>2.9733</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1793</v>
+        <v>1.4821</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4172</v>
+        <v>0.3985</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7621</v>
+        <v>1.0836</v>
       </c>
       <c r="V16" t="n">
         <v>1.4033</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9069</v>
+        <v>0.7454</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8973</v>
+        <v>-0.9829</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8042</v>
+        <v>1.7283</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5697</v>
+        <v>1.0953</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.1841</v>
+        <v>-1.1471</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6143</v>
+        <v>2.2424</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6674</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1288</v>
+        <v>-1.089</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4614</v>
+        <v>1.02</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9023</v>
+        <v>1.1643</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0552</v>
+        <v>-0.0581</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1529</v>
+        <v>1.2224</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.1538</v>
+        <v>-1.3876</v>
       </c>
       <c r="R17" t="n">
-        <v>3.568</v>
+        <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1814</v>
+        <v>0.2625</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8468</v>
+        <v>0.4737</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3346</v>
+        <v>-0.2112</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8811</v>
+        <v>-1.2071</v>
       </c>
       <c r="W17" t="n">
-        <v>2.0772</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1962</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MUNOZ MENDOZA</t>
+          <t>S. CASTRO BRAVO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5695</v>
+        <v>0.4472</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5614</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1309</v>
+        <v>1.3721</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.635</v>
+        <v>0.0076</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7579</v>
+        <v>0.4936</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1229</v>
+        <v>-0.486</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5469</v>
+        <v>-0.289</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.7076</v>
+        <v>0.3499</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1607</v>
+        <v>-0.639</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9119</v>
+        <v>0.2966</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0503</v>
+        <v>0.1437</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.1529</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1893</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5769</v>
+        <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2906</v>
+        <v>0.3781</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1749</v>
+        <v>0.5535</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1158</v>
+        <v>-0.1754</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4737</v>
+        <v>-0.5331</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4737</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3904</v>
+        <v>-3.0178</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3117</v>
+        <v>3.2678</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0953</v>
+        <v>-1.5697</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1471</v>
+        <v>-2.1841</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2424</v>
+        <v>0.6143</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.6674</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.089</v>
+        <v>-1.1288</v>
       </c>
       <c r="L20" t="n">
-        <v>1.02</v>
+        <v>0.4614</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1643</v>
+        <v>-0.9023</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0581</v>
+        <v>-1.0552</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2224</v>
+        <v>0.1529</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5947</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3876</v>
+        <v>-5.1538</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9822</v>
+        <v>3.568</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5616</v>
+        <v>1.5244</v>
       </c>
       <c r="T20" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.7262</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6278</v>
+        <v>0.7982</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2071</v>
+        <v>1.8811</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.0772</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2071</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>J. MUNOZ MENDOZA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0945</v>
+        <v>0.0406</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.59</v>
+        <v>-1.9689</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4955</v>
+        <v>2.0095</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7065</v>
+        <v>-0.635</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6477</v>
+        <v>-1.7579</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9412</v>
+        <v>1.1229</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1974</v>
+        <v>-1.5469</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3179</v>
+        <v>-1.7076</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1205</v>
+        <v>0.1607</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4909</v>
+        <v>0.9119</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3298</v>
+        <v>-0.0503</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8207</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1893</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3876</v>
+        <v>2.5769</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4137</v>
+        <v>0.7617</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7967</v>
+        <v>0.7674</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.383</v>
+        <v>-0.0057</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. CASTRO BRAVO</t>
+          <t>L. MORENO MORALES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6662</v>
+        <v>-0.0582</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8417</v>
+        <v>-1.3995</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1755</v>
+        <v>1.3413</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0076</v>
+        <v>-4.1943</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4936</v>
+        <v>-0.3873</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.486</v>
+        <v>-3.807</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.289</v>
+        <v>-2.8222</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3499</v>
+        <v>0.6059</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.639</v>
+        <v>-3.428</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2966</v>
+        <v>-1.3722</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1437</v>
+        <v>-0.9932</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1529</v>
+        <v>-0.379</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5947</v>
+        <v>2.3787</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.784</v>
+        <v>2.3787</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7353</v>
+        <v>-0.0532</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3634</v>
+        <v>-0.388</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3719</v>
+        <v>0.3348</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5331</v>
+        <v>1.8107</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. MORENO MORALES</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0566</v>
+        <v>-0.2127</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7051</v>
+        <v>-1.8956</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6485</v>
+        <v>1.6829</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.1943</v>
+        <v>-0.7065</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3873</v>
+        <v>-1.6477</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.807</v>
+        <v>0.9412</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.8222</v>
+        <v>-1.1974</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6059</v>
+        <v>-1.3179</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.428</v>
+        <v>0.1205</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3722</v>
+        <v>0.4909</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9932</v>
+        <v>-0.3298</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.379</v>
+        <v>0.8207</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3787</v>
+        <v>0.1982</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3787</v>
+        <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0516</v>
+        <v>0.2955</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6936</v>
+        <v>0.4911</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.358</v>
+        <v>-0.1956</v>
       </c>
       <c r="V23" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.147</v>
+        <v>-1.0628</v>
       </c>
       <c r="E24" t="n">
         <v>-0.0624</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0846</v>
+        <v>-1.0004</v>
       </c>
       <c r="G24" t="n">
         <v>0.0039</v>
@@ -2326,13 +2326,13 @@
         <v>0.1982</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1421</v>
+        <v>-0.0578</v>
       </c>
       <c r="T24" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.0046</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2071</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0628</v>
+        <v>-2.3382</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8605</v>
+        <v>-3.7399</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7977</v>
+        <v>1.4017</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7549</v>
@@ -2404,13 +2404,13 @@
         <v>3.1716</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.4972</v>
+        <v>-0.7726</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.6223</v>
+        <v>-0.5018</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8749</v>
+        <v>-0.2709</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6036</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.2286</v>
+        <v>-4.9347</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.011</v>
+        <v>-5.9091</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7824</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-3.187</v>
@@ -2482,13 +2482,13 @@
         <v>1.784</v>
       </c>
       <c r="S26" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.3644</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3192</v>
+        <v>-0.2174</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3898</v>
+        <v>0.5817</v>
       </c>
       <c r="V26" t="n">
         <v>0.2666</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.0479</v>
+        <v>-3.0105</v>
       </c>
       <c r="E27" t="n">
-        <v>-17.6676</v>
+        <v>-17.6675</v>
       </c>
       <c r="F27" t="n">
-        <v>12.6197</v>
+        <v>14.657</v>
       </c>
       <c r="G27" t="n">
         <v>-10.5059</v>
@@ -2539,7 +2539,7 @@
         <v>-7.9375</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.1709999999999997</v>
+        <v>-0.171</v>
       </c>
       <c r="M27" t="n">
         <v>-2.3976</v>
@@ -2551,7 +2551,7 @@
         <v>2.8591</v>
       </c>
       <c r="P27" t="n">
-        <v>2.9734</v>
+        <v>2.973399999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>-18.8312</v>
@@ -2560,19 +2560,19 @@
         <v>21.8045</v>
       </c>
       <c r="S27" t="n">
-        <v>2.147699999999999</v>
+        <v>4.1851</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2409</v>
+        <v>2.2408</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.09299999999999981</v>
+        <v>1.9441</v>
       </c>
       <c r="V27" t="n">
         <v>0.3370999999999997</v>
       </c>
       <c r="W27" t="n">
-        <v>7.0315</v>
+        <v>7.031500000000001</v>
       </c>
       <c r="X27" t="n">
         <v>-6.694400000000001</v>
